--- a/Control_GastosV2/reportes/Reporte_2026_04_2026-04-03.xlsx
+++ b/Control_GastosV2/reportes/Reporte_2026_04_2026-04-03.xlsx
@@ -416,7 +416,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D9"/>
+  <dimension ref="A1:D20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -578,7 +578,7 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>77111.52</v>
+        <v>77112</v>
       </c>
     </row>
     <row r="9">
@@ -598,7 +598,227 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>14356.2</v>
+        <v>14356</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Canal Flow</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>PerFlow</t>
+        </is>
+      </c>
+      <c r="D10" t="n">
+        <v>60967</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Luz</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Eden</t>
+        </is>
+      </c>
+      <c r="D11" t="n">
+        <v>135217</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>2026-04-06</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Gas</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Litoral Cas</t>
+        </is>
+      </c>
+      <c r="D12" t="n">
+        <v>12040</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>2026-04-09</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Tracker</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>PatAuto</t>
+        </is>
+      </c>
+      <c r="D13" t="n">
+        <v>49839</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Municipal</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>TasaTDU</t>
+        </is>
+      </c>
+      <c r="D14" t="n">
+        <v>34933</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>2026-04-10</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>Agua Corriente</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>TasaTSS</t>
+        </is>
+      </c>
+      <c r="D15" t="n">
+        <v>27406</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>Impuesto Prov</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Inmobiliario</t>
+        </is>
+      </c>
+      <c r="D16" t="n">
+        <v>23559</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2026-04-01</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>Tel Mig y Bel</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Celulares</t>
+        </is>
+      </c>
+      <c r="D17" t="n">
+        <v>62748</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2026-04-12</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>tracker</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>SegAuto</t>
+        </is>
+      </c>
+      <c r="D18" t="n">
+        <v>95233</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2026-04-17</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>casa</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>SegCasa</t>
+        </is>
+      </c>
+      <c r="D19" t="n">
+        <v>21910</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2026-04-14</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>banco prov.</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>SegBanco</t>
+        </is>
+      </c>
+      <c r="D20" t="n">
+        <v>17100</v>
       </c>
     </row>
   </sheetData>
@@ -750,7 +970,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>376158.72</v>
+        <v>917111</v>
       </c>
     </row>
     <row r="4">
@@ -760,7 +980,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3419697.15</v>
+        <v>2878744.87</v>
       </c>
     </row>
   </sheetData>
@@ -774,7 +994,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B20"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -802,71 +1022,181 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Farmacia</t>
+          <t>Celulares</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>12000</v>
+        <v>62748</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>MasterCard</t>
+          <t>Eden</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>14356.2</v>
+        <v>135217</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Nafta</t>
+          <t>Farmacia</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>30646</v>
+        <v>12000</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Psicólogo</t>
+          <t>Inmobiliario</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>120000</v>
+        <v>23559</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Supermercado</t>
+          <t>Litoral Cas</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>82335</v>
+        <v>12040</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Verdulería</t>
+          <t>MasterCard</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>25210</v>
+        <v>14356</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Nafta</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>30646</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>PatAuto</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>49839</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>PerFlow</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>60967</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>Psicólogo</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>120000</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>SegAuto</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>95233</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>SegBanco</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>17100</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>SegCasa</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>21910</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Supermercado</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>82335</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>TasaTDU</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>34933</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>TasaTSS</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>27406</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Verdulería</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>25210</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
           <t>Visa</t>
         </is>
       </c>
-      <c r="B9" t="n">
-        <v>77111.52</v>
+      <c r="B20" t="n">
+        <v>77112</v>
       </c>
     </row>
   </sheetData>
